--- a/test/evaluation/cvs.xlsx
+++ b/test/evaluation/cvs.xlsx
@@ -31,7 +31,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -46,6 +46,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0063BE7B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -71,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -86,6 +91,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -633,7 +641,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>85</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -643,7 +651,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Incluye todos los 9 candidatos esperados (Alice, Ann, Cameron, Jack, Jason, Julian, Katherine, Olga, Sanjay).</t>
+          <t>Incluye todos los candidatos esperados. Contiene además perfiles adicionales y varios marcados como 'No Elasticsearch mentioned', lo que añade ruido.</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -653,12 +661,12 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>0.00068595</t>
+          <t>0.00063925</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>0.04281395</t>
+          <t>0.04276725</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr"/>
@@ -725,7 +733,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -735,7 +743,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Lista exacta de los 7 candidatos esperados (Maria, Marilyn, Jack, Stephanie, Olga, Jonathan, Olivia).</t>
+          <t>Lista exactamente los 7 candidatos esperados, sin omisiones ni información irrelevante.</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -745,12 +753,12 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>0.00068595</t>
+          <t>0.00063925</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>0.04446995</t>
+          <t>0.04442325</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr"/>
@@ -816,7 +824,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -826,7 +834,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Contiene los 6 candidatos esperados (Ahmed, Charles, Ibrahim, Kayla, Kimberly, Melissa).</t>
+          <t>Coincide plenamente con los 6 candidatos esperados; respuesta clara y directa.</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -836,12 +844,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0.00068595</t>
+          <t>0.00063925</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0.04069295</t>
+          <t>0.04064625</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr"/>
@@ -907,7 +915,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -917,7 +925,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Contiene los 6 candidatos esperados (Caleb, Edward, Elijah, Owen, Pradeep, William).</t>
+          <t>Incluye exactamente los 6 candidatos esperados con mención clara de Apache Kafka.</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -927,12 +935,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0.00068595</t>
+          <t>0.00063925</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0.0442287</t>
+          <t>0.044182</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr"/>
@@ -1022,7 +1030,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>85</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -1032,7 +1040,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>De 35 esperados, aparecen 27 en la respuesta real; faltan varios (p.ej. Alice MacGregor King, Connor Maxwell Johnson, Nathan King Palmer, varias 'Nicole').</t>
+          <t>Cubre 30 de 35 esperados (~77%). Responde directamente, pero omite varios nombres y añade algunos perfiles extra.</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1042,12 +1050,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0.00068595</t>
+          <t>0.00063925</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0.0445322</t>
+          <t>0.0444855</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr"/>
@@ -1115,7 +1123,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -1125,7 +1133,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Incluye los 8 candidatos esperados (Alan, Ashley, Brenda, Chase, Hassan, Judith, Parker, Patrick).</t>
+          <t>Lista los 8 candidatos esperados exactamente; respuesta completa y pertinente.</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1135,12 +1143,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0.00068595</t>
+          <t>0.00063925</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0.04468245</t>
+          <t>0.04463575</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr"/>
@@ -1205,7 +1213,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -1215,7 +1223,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Contiene los 5 candidatos esperados (Elizabeth, Emma, Jack, Ronald, Sara).</t>
+          <t>Coincide con la lista esperada de 5 candidatos; respuesta directa y completa.</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1225,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0.00068595</t>
+          <t>0.00063925</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0.04350595</t>
+          <t>0.04345925</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr"/>
@@ -1295,7 +1303,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -1305,7 +1313,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Lista completa de los 5 candidatos esperados (Aaron, Bradley, Cameron, Sarah Perez, Sarah Woods).</t>
+          <t>Incluye los 5 candidatos esperados, con mención explícita de Event-Driven Architecture.</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1315,12 +1323,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0.00068595</t>
+          <t>0.00063925</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0.06828145</t>
+          <t>0.06823475</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr"/>
@@ -1383,7 +1391,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -1393,7 +1401,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Contiene los 4 candidatos esperados para iOS Developer (Gerald, Kimberly, Landon, Sarah).</t>
+          <t>Respuesta coincide exactamente con los 4 candidatos registrados como iOS Developer.</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1403,12 +1411,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0.00068595</t>
+          <t>0.00063925</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0.04737195</t>
+          <t>0.04732525</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr"/>
@@ -1471,7 +1479,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -1481,7 +1489,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Incluye los 4 candidatos esperados para PhD Researcher (Ahmed, Melissa, Russell, Walter).</t>
+          <t>Incluye exactamente los 4 perfiles esperados registrados como PhD Researcher.</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1491,12 +1499,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0.00068595</t>
+          <t>0.00063925</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0.0544662</t>
+          <t>0.0544195</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr"/>
@@ -1558,7 +1566,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -1568,7 +1576,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Incluye las 3 personas esperadas: Arjun Foster Gutierrez, Liam Clark Jackson y Nancy Morales Cooper.</t>
+          <t>Contiene exactamente las tres personas esperadas (Arjun, Liam, Nancy) y responde de forma clara.</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1578,12 +1586,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0.0014267</t>
+          <t>0.00093025</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0.05647995</t>
+          <t>0.0559835</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr"/>
@@ -1644,7 +1652,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -1654,7 +1662,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Incluye ambos perfiles esperados: Bruce O'Connor O'Brien y Ming Bell Rose.</t>
+          <t>Incluye las dos personas esperadas (Bruce, Ming) y responde de manera directa y completa.</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1664,12 +1672,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0.0014267</t>
+          <t>0.00093025</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0.05285495</t>
+          <t>0.0523585</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr"/>
@@ -1735,7 +1743,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -1745,7 +1753,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Contiene los 3 esperados (Chen Phillips Mensah, Evelyn Tran Morgan, Rohan Sanders Ashworth); añade además 3 perfiles adicionales.</t>
+          <t>Cubre las tres personas esperadas (Chen, Rohan, Evelyn); añade perfiles adicionales pero responde correctamente.</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1755,12 +1763,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0.0014267</t>
+          <t>0.00093025</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0.0525762</t>
+          <t>0.05207975</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr"/>
@@ -1824,7 +1832,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -1834,7 +1842,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Contiene los 2 esperados (Maria Ashworth Roberts y Jonathan Tran Henry) y además muestra 2 perfiles adicionales.</t>
+          <t>Incluye los dos candidatos esperados (Maria, Jonathan) y aporta otros coincidentes; responde directamente.</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1844,12 +1852,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0.0014267</t>
+          <t>0.00093025</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0.05311395</t>
+          <t>0.0526175</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr"/>
@@ -1972,12 +1980,12 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>85</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>90</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -1987,7 +1995,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Encontró 68/75 perfiles esperados; faltan 7 nombres (p.ej. Grace Choi Lowe, Hannah Jones Mendoza, Jennifer Peterson Moseley, Kayla Gomez Maddox, Luke Lane James, Samantha Reddy Kennedy, Teresa Graham Lopez).</t>
+          <t>Lista 68 perfiles e incluye la mayoría de los esperados, pero omite varios nombres de la lista esperada.</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1997,12 +2005,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0.0014267</t>
+          <t>0.00093025</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0.0594257</t>
+          <t>0.05892925</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr"/>
@@ -2102,12 +2110,12 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>80</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>90</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -2117,7 +2125,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Encontró 45/57 perfiles esperados (≈79%); faltan varios nombres clave como Arjun Foster Gutierrez, Bryan Sanders Taylor, Rohan Sanders Ashworth, entre otros.</t>
+          <t>Devuelve 45 perfiles cubriendo gran parte de la lista esperada; faltan varios candidatos esperados.</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2127,12 +2135,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0.0014267</t>
+          <t>0.00093025</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0.0636517</t>
+          <t>0.06315525</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr"/>
@@ -2197,12 +2205,12 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>85</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -2212,7 +2220,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Encontró 10/13 perfiles esperados (≈77%); faltan Chase Edwards Campbell, Fatima Burns Cunningham y Gavin Cox Diaz.</t>
+          <t>Incluye 10 de 13 esperados; faltan Chase Edwards Campbell, Fatima Burns Cunningham y Gavin Cox Diaz.</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2222,12 +2230,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0.0014267</t>
+          <t>0.00093025</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>0.0469127</t>
+          <t>0.04641625</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr"/>
@@ -2298,7 +2306,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>90</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -2308,7 +2316,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Encontró 11/13 perfiles esperados (≈85%); faltan Austin Morales Singh y Natalie Sutton Burke.</t>
+          <t>Lista 11/13 esperados; faltan Austin Morales Singh y Natalie Sutton Burke; respuesta clara y pertinente.</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2318,12 +2326,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0.0014267</t>
+          <t>0.00093025</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0.04631845</t>
+          <t>0.045822</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr"/>
@@ -2404,7 +2412,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
@@ -2414,7 +2422,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Incluye todos los perfiles esperados para japonés (cubre la lista completa de candidatos mencionados).</t>
+          <t>Cubre todos los candidatos esperados (todos aparecen) y responde exactamente a la pregunta.</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2424,12 +2432,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0.0014267</t>
+          <t>0.00093025</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0.0508907</t>
+          <t>0.05039425</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr"/>
@@ -2509,7 +2517,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>95</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
@@ -2519,7 +2527,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Encontró 18/19 perfiles esperados (≈95%); sólo falta Jonathan Tran Henry; además aparecen 2 perfiles extra no esperados.</t>
+          <t>Incluye casi todos los 19 esperados (faltó Jonathan Tran Henry) y añade dos perfiles extra; muy relevante.</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2529,12 +2537,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0.0014267</t>
+          <t>0.00093025</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0.04649345</t>
+          <t>0.045997</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr"/>
@@ -2653,7 +2661,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>90</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -2663,7 +2671,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>Los 21 candidatos esperados aparecen en la respuesta real; además incluye muchos perfiles adicionales.</t>
+          <t>Incluye todas las 21 esperadas y además muchos perfiles relacionados (hybrid/remote_collaboration). Completa pero algo sobre-inclusiva.</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2673,12 +2681,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0.0005952</t>
+          <t>0.0006445</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0.0569257</t>
+          <t>0.056975</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr"/>
@@ -2750,7 +2758,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
@@ -2760,7 +2768,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>Los 12 candidatos esperados aparecen exactamente en la respuesta real.</t>
+          <t>Lista exactamente las 12 esperadas, responde de forma precisa y completa.</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2770,12 +2778,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0.0005952</t>
+          <t>0.0006445</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0.04933345</t>
+          <t>0.04938275</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr"/>
@@ -2855,7 +2863,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -2865,7 +2873,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>Los 20 candidatos esperados aparecen exactamente en la respuesta real.</t>
+          <t>Coincide exactamente con las 20 esperadas y responde directamente a la pregunta.</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2875,12 +2883,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0.0005952</t>
+          <t>0.0006445</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0.03746145</t>
+          <t>0.03751075</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr"/>
@@ -2984,7 +2992,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>90</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
@@ -2994,7 +3002,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>Aparecen 20 de 21 candidatos esperados; falta 'Devon Evans Lane'.</t>
+          <t>Incluye la gran mayoría de los esperados (faltó Devon Evans Lane) y muchos adicionales; respuesta relevante pero no totalmente completa.</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3004,12 +3012,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0.0005952</t>
+          <t>0.0006445</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0.05313245</t>
+          <t>0.05318175</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr"/>
@@ -3081,7 +3089,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
@@ -3091,7 +3099,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>Los 9 candidatos esperados aparecen en la respuesta real; además hay 3 perfiles extra.</t>
+          <t>Incluye todas las entidades esperadas y añade perfiles adicionales pertinentes; responde correctamente.</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3101,12 +3109,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0.0005952</t>
+          <t>0.0006445</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0.04110245</t>
+          <t>0.04115175</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr"/>
@@ -3164,7 +3172,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -3174,7 +3182,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>Ninguno de los 3 candidatos esperados fue devuelto en la respuesta real.</t>
+          <t>No devolvió ninguno de los 3 perfiles esperados; omite completamente la información solicitada.</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3184,12 +3192,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0.0005952</t>
+          <t>0.0006445</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>0.04271745</t>
+          <t>0.04276675</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr"/>
@@ -3245,12 +3253,12 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
@@ -3260,7 +3268,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>Solo 2 de 7 candidatos esperados aparecen (Bryan Sanders Taylor, Cameron Palmer Brennan); faltan 5.</t>
+          <t>Encontró solo 2 de 7 esperados (Bryan y Cameron). Información correcta pero claramente incompleta.</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3270,12 +3278,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0.0005952</t>
+          <t>0.0006445</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0.0587812</t>
+          <t>0.0588305</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr"/>
@@ -3333,7 +3341,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -3343,7 +3351,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>No aparece la candidata esperada ('Sarah Woods Kelley').</t>
+          <t>No encontró al candidato esperado (Sarah Woods Kelley); no responde a la pregunta.</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3353,12 +3361,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0.0005952</t>
+          <t>0.0006445</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0.06656945</t>
+          <t>0.06661875</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr"/>
@@ -3416,7 +3424,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
@@ -3426,7 +3434,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>No aparece el candidato esperado ('Austin Morales Singh').</t>
+          <t>No encontró al candidato esperado (Austin Morales Singh); omisión total de la respuesta esperada.</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3436,12 +3444,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0.0005952</t>
+          <t>0.0006445</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0.0656372</t>
+          <t>0.0656865</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr"/>
@@ -3499,7 +3507,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -3509,7 +3517,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>Ninguno de los dos candidatos esperados aparece ('Christopher Miller Watson', 'Jean Jimenez Mbeki').</t>
+          <t>No encontró a los candidatos esperados (Christopher Miller Watson, Jean Jimenez Mbeki); respuesta vacía.</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3519,12 +3527,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0.0005952</t>
+          <t>0.0006445</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0.05853795</t>
+          <t>0.05858725</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr"/>
@@ -3587,7 +3595,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>85</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -3597,7 +3605,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>Incluye los dos candidatos esperados (Arjun, Beverly) pero añade dos perfiles adicionales incorrectos (Lori, Benjamin), por lo que hay exceso de falsos positivos.</t>
+          <t>Incluye ambos candidatos esperados (Arjun, Beverly) pero añade dos falsos positivos (Lori, Benjamin), por lo que no coincide exactamente.</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3607,12 +3615,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0.00025395</t>
+          <t>0.00048125</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0.0711412</t>
+          <t>0.0713685</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr"/>
@@ -3670,17 +3678,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="L33" s="4" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>La respuesta real no encontró ningún perfil, omitiendo completamente al candidato esperado Caleb Rodriguez Armstrong.</t>
+          <t>No incluye al candidato esperado (Caleb) y afirma que no hay coincidencias; es una respuesta directa al filtro aunque incorrecta respecto al gold.</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -3690,12 +3698,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0.00025395</t>
+          <t>0.00048125</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>0.07308795</t>
+          <t>0.07331525</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr"/>
@@ -3753,17 +3761,17 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>No se encontraron perfiles en la respuesta real, omitiendo por completo al candidato esperado William Freeman Allen.</t>
+          <t>Omite al candidato esperado (William) y reporta 'no matches'; responde directamente a la consulta aunque difiere del estándar.</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3773,12 +3781,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0.00025395</t>
+          <t>0.00048125</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0.07335745</t>
+          <t>0.07358475</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr"/>
@@ -3841,17 +3849,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="L35" s="4" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>La respuesta real lista cuatro candidatos distintos y no incluye al candidato esperado Sara Simmons Grant; falla en identificar la entidad requerida.</t>
+          <t>No incluye a la persona esperada (Sara), pero lista cuatro perfiles que satisfacen el criterio: respuesta coherente pero no coincide con el gold.</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3861,12 +3869,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0.00025395</t>
+          <t>0.00048125</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>0.05916245</t>
+          <t>0.05938975</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr"/>
@@ -3930,7 +3938,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -3940,7 +3948,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>La respuesta real contiene exactamente los cuatro nombres esperados (Brenda, Fatima, Theresa, William) y la información solicitada.</t>
+          <t>Contiene exactamente las cuatro personas esperadas (Brenda, Fatima, Theresa, William) y responde directamente a la pregunta.</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3950,12 +3958,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0.00025395</t>
+          <t>0.00048125</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0.04254545</t>
+          <t>0.04277275</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr"/>
@@ -4013,17 +4021,17 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>La respuesta real no encontró perfiles, omitiendo completamente a los tres candidatos esperados (Arjun, Gerald, Sarah).</t>
+          <t>No incluye a los candidatos esperados (Arjun, Gerald, Sarah) y dice que no hay coincidencias; es una respuesta directa aunque discrepante.</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4033,12 +4041,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0.00025395</t>
+          <t>0.00048125</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>0.04716645</t>
+          <t>0.04739375</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr"/>
@@ -4098,7 +4106,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -4108,7 +4116,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>Coincide exactamente: encuentra a Cole Kim Yamamoto y confirma italiano y trabajo remoto en el CV.</t>
+          <t>Incluye exactamente a Cole Kim Yamamoto y confirma que habla italiano y menciona trabajo remoto; cumple plenamente.</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4118,12 +4126,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0.00025395</t>
+          <t>0.00048125</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>0.05070595</t>
+          <t>0.05093325</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr"/>
@@ -4181,7 +4189,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
@@ -4191,7 +4199,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>La respuesta real indica que no hay perfiles, que coincide con la respuesta esperada (lista vacía).</t>
+          <t>Respuesta indica que no hay perfiles; el gold espera lista vacía, por tanto coincide y es pertinente.</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4201,12 +4209,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0.00025395</t>
+          <t>0.00048125</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>0.0507722</t>
+          <t>0.0509995</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr"/>
@@ -4266,7 +4274,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -4276,7 +4284,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>Coincide exactamente: encuentra a Charlotte Lawrence Gallagher con experiencia en startups y hackathons.</t>
+          <t>Incluye exactamente a Charlotte Lawrence Gallagher con ambos atributos (startups y hackathons); responde correctamente.</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4286,12 +4294,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0.00025395</t>
+          <t>0.00048125</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>0.04966745</t>
+          <t>0.04989475</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr"/>
@@ -4349,7 +4357,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
@@ -4359,7 +4367,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>La respuesta real no encuentra perfiles, coincidiendo con la respuesta esperada (ningún candidato).</t>
+          <t>Respuesta indica que no hay coincidencias; el gold espera vacío, así que coincide y es pertinente.</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4369,12 +4377,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0.00025395</t>
+          <t>0.00048125</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>0.0591377</t>
+          <t>0.059365</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr"/>
@@ -4432,7 +4440,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
@@ -4442,7 +4450,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>Respuesta real indica "no matching profiles" coincidiendo exactamente con la esperada (lista vacía).</t>
+          <t>La respuesta real indica que no hay perfiles coincidentes, igual que la respuesta esperada (ninguno).</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -4452,12 +4460,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0.00075395</t>
+          <t>0.00066725</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>0.04715995</t>
+          <t>0.04707325</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr"/>
@@ -4520,22 +4528,22 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="L43" s="4" t="inlineStr">
+          <t>80</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>Real incluye 9 de 22 nombres esperados (Gabriel, Carol, Maria, Margaret, Bryan, Emma W., Henry, Daniel, Emma L.); faltan muchos.</t>
+          <t>La real aporta 9 de 22 nombres esperados (p.ej. Gabriel, Carol, Maria, Margaret, Bryan, Emma W, Henry, Daniel, Emma L); faltan 13 nombres.</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -4545,12 +4553,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0.00075395</t>
+          <t>0.00066725</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>0.0468327</t>
+          <t>0.046746</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr"/>
@@ -4608,7 +4616,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
@@ -4618,7 +4626,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>Esperaban 3 nombres; la respuesta real no encontró coincidencias y omitió todos los esperados.</t>
+          <t>La real dice que no hay coincidencias pero la esperada contiene 3 perfiles; omite completamente la información esperada.</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -4628,12 +4636,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0.00075395</t>
+          <t>0.00066725</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>0.0533007</t>
+          <t>0.053214</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr"/>
@@ -4706,7 +4714,7 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>90</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
@@ -4716,7 +4724,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>La respuesta real incluye los 4 nombres esperados (Ashley, Frank, Sanjay, William) además de varios adicionales.</t>
+          <t>Incluye los cuatro esperados (Sanjay, William, Frank, Ashley) y además 9 perfiles adicionales; cubre totalmente lo solicitado.</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -4726,12 +4734,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>0.00075395</t>
+          <t>0.00066725</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>0.0399247</t>
+          <t>0.039838</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr"/>
@@ -4794,7 +4802,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
@@ -4804,7 +4812,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>De 3 esperados solo aparece Pradeep en la respuesta real; faltan Jack y Priya (cobertura parcial baja).</t>
+          <t>Aparece solo Pradeep de los 3 esperados; la real devuelve 4 perfiles en total, por tanto cobertura parcial y respuestas pertinentes.</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -4814,12 +4822,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0.00075395</t>
+          <t>0.00066725</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>0.04258195</t>
+          <t>0.04249525</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr"/>
@@ -4880,17 +4888,17 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="L47" s="4" t="inlineStr">
+          <t>80</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>Esperaban Isabella Stone Jenkins; la respuesta real lista otras dos personas distintas y no incluye a Isabella.</t>
+          <t>No incluye a Isabella (esperada), pero ofrece dos perfiles relevantes que cumplen experiencia en agile y APIs; responde la consulta aunque difiera del gold.</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -4900,12 +4908,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0.00075395</t>
+          <t>0.00066725</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>0.0366462</t>
+          <t>0.0365595</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr"/>
@@ -5059,14 +5067,14 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
           <t>OK</t>
@@ -5074,7 +5082,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>Respuesta real devuelve 99 perfiles y coincide con la gran mayoría de los nombres esperados, faltan pocos elementos menores.</t>
+          <t>La real lista 99 perfiles y coincide con la mayor parte de la lista esperada (alta cobertura); responde directamente a 'French OR Microservices'.</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5084,12 +5092,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0.00075395</t>
+          <t>0.00066725</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>0.0443012</t>
+          <t>0.0442145</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr"/>
@@ -5204,12 +5212,12 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>90</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>95</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
@@ -5219,7 +5227,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>Respuesta real incluye casi todas las entidades esperadas (60 perfiles); solo faltan contadas entradas menores.</t>
+          <t>La real devuelve 60 perfiles y cubre la mayoría de los esperados, incluyendo both German speakers y expertos en Kafka; muy pertinente.</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5229,12 +5237,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0.00075395</t>
+          <t>0.00066725</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>0.05213045</t>
+          <t>0.05204375</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr"/>
@@ -5310,7 +5318,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
@@ -5320,7 +5328,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>La respuesta real lista exactamente los 16 perfiles esperados (todos presentes).</t>
+          <t>Coincidencia exacta: 16 perfiles listados en la real coinciden con los 16 esperados; responde directamente a la consulta.</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5330,12 +5338,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0.00075395</t>
+          <t>0.00066725</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>0.0499757</t>
+          <t>0.049889</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr"/>
@@ -5419,7 +5427,7 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
@@ -5429,7 +5437,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>La respuesta real incluye todos los nombres esperados (además de algunos adicionales), cobertura completa.</t>
+          <t>La real incluye los 22 esperados y añade 2 más (24 en total); cubre completamente la información solicitada y responde correctamente.</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -5439,12 +5447,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>0.00075395</t>
+          <t>0.00066725</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>0.05270995</t>
+          <t>0.05262325</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr"/>
@@ -5529,7 +5537,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
@@ -5539,7 +5547,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>La respuesta real incluye exactamente los 25 perfiles esperados; cobertura completa.</t>
+          <t>Listado coincide exactamente con las 25 entidades esperadas y señala la razón (idioma/skill) para cada perfil.</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -5549,12 +5557,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0.0009047</t>
+          <t>0.00070025</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>0.0498597</t>
+          <t>0.04965525</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr"/>
@@ -5625,7 +5633,7 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
@@ -5635,7 +5643,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>La respuesta real contiene los 11 perfiles esperados; coincidencia completa.</t>
+          <t>Incluye las 11 entidades esperadas y especifica si es por ruso o BERT; cobertura completa y relevante.</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -5645,12 +5653,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0.0009047</t>
+          <t>0.00070025</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>0.05143645</t>
+          <t>0.051232</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr"/>
@@ -5719,7 +5727,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>90</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
@@ -5729,7 +5737,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>Se encontraron 9 de 12 perfiles esperados; faltan Ann Park Glover, DeShawn Gray Brennan y Diane Evans Al-Farsi.</t>
+          <t>Encontró 9 de 12 perfiles esperados; faltan Ann Park Glover, DeShawn Gray Brennan y Diane Evans Al‑Farsi, pero responde correctamente.</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -5739,12 +5747,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>0.0009047</t>
+          <t>0.00070025</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>0.05624945</t>
+          <t>0.056045</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr"/>
@@ -5847,7 +5855,7 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
@@ -5857,7 +5865,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>La respuesta real incluye todos los ~40 perfiles de la lista esperada (más algunos extras); cobertura completa.</t>
+          <t>Cubre todos los candidatos esperados (incluso aporta algunos adicionales); respuesta completa y pertinente.</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -5867,12 +5875,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0.0009047</t>
+          <t>0.00070025</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>0.05052245</t>
+          <t>0.050318</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr"/>
@@ -5941,7 +5949,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
@@ -5951,7 +5959,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>Se encontraron los 9 perfiles esperados; coincidencia completa.</t>
+          <t>Lista las 9 entidades esperadas y indica claramente si conocen Django o Flask; cobertura completa.</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -5961,12 +5969,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0.0009047</t>
+          <t>0.00070025</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>0.04072095</t>
+          <t>0.0405165</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr"/>
@@ -6045,7 +6053,7 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
@@ -6055,7 +6063,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>La respuesta real incluye los 15 perfiles esperados (y unos extras); cobertura completa.</t>
+          <t>Incluye todos los candidatos esperados (y añade perfiles extra); responde exactamente a la consulta.</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6065,12 +6073,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>0.0009047</t>
+          <t>0.00070025</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>0.04681245</t>
+          <t>0.046608</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr"/>
@@ -6145,7 +6153,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
@@ -6155,7 +6163,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>La respuesta real cubre los 9 perfiles esperados (con perfiles adicionales); coincidencia total.</t>
+          <t>Contiene las 9 entidades esperadas y más; menciona OpenCV o BERT para cada uno, muy relevante.</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6165,12 +6173,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>0.0009047</t>
+          <t>0.00070025</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>0.0522022</t>
+          <t>0.05199775</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr"/>
@@ -6239,7 +6247,7 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
@@ -6249,7 +6257,7 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>La respuesta real incluye los 9 perfiles esperados exactamente; cobertura completa.</t>
+          <t>Presenta las 9 entradas esperadas y la razón (Airflow/Glue) para cada perfil; cobertura y relevancia completas.</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -6259,12 +6267,12 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>0.0009047</t>
+          <t>0.00070025</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>0.04902295</t>
+          <t>0.0488185</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr"/>
@@ -6337,7 +6345,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
@@ -6347,7 +6355,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>La respuesta real contiene los 13 perfiles esperados; coincidencia completa.</t>
+          <t>Incluye las 13 entidades esperadas, indicando WebSockets o gRPC para cada perfil; respuesta precisa.</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -6357,12 +6365,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>0.0009047</t>
+          <t>0.00070025</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>0.0453272</t>
+          <t>0.04512275</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr"/>
@@ -6452,12 +6460,12 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>90</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>95</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
@@ -6467,7 +6475,7 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>Se encontraron 35 de 38 perfiles esperados; faltan Jonathan Tran Henry, Emma Wells Russell y Kathleen Taylor Edwards.</t>
+          <t>Encontró 35 de ~38 perfiles esperados; omite a Jonathan Tran Henry, Emma Wells Russell y Samantha Ford Nkosi, pero responde bien.</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -6477,12 +6485,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>0.0009047</t>
+          <t>0.00070025</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>0.0511032</t>
+          <t>0.05089875</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr"/>
@@ -6583,12 +6591,12 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>85</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>95</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
@@ -6598,7 +6606,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>La respuesta real incluye 28/31 candidatos esperados (faltan Ethan Buchanan Evans, Mark Thompson Turner, Michael Cruz Gonzales); además añade perfiles extra.</t>
+          <t>Cubre la mayoría de las entidades esperadas (faltan pocos nombres) e incluye perfiles adicionales válidos; respuesta directa y completa en esencia.</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -6608,12 +6616,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>0.0009782</t>
+          <t>0.0008015</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>0.05724945</t>
+          <t>0.05707275</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr"/>
@@ -6690,7 +6698,7 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr">
@@ -6700,7 +6708,7 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>Coincidencia completa: la lista real contiene los 17 candidatos esperados y ningún omisión evidente.</t>
+          <t>Lista de 17 perfiles coincide con la esperada exactamente; responde claramente a la pregunta sobre fintech o banking.</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -6710,12 +6718,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>0.0009782</t>
+          <t>0.0008015</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>0.0521202</t>
+          <t>0.0519435</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr"/>
@@ -6873,12 +6881,12 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>100</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
@@ -6888,7 +6896,7 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>La respuesta real devuelve 103 perfiles y cubre la gran mayoría de los esperados; solo pequeñas discrepancias/omisiones menores.</t>
+          <t>Coincide con la lista extensa esperada (103 perfiles) y responde directamente quiénes hablan francés o alemán.</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -6898,12 +6906,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>0.0009782</t>
+          <t>0.0008015</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>0.03312795</t>
+          <t>0.03295125</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr"/>
@@ -6989,7 +6997,7 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L65" s="3" t="inlineStr">
@@ -6999,7 +7007,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>Coincidencia completa: la respuesta real contiene los 26 candidatos esperados (todos presentes).</t>
+          <t>Incluye las entidades esperadas (más un perfil extra) y responde claramente quiénes hablan italiano o portugués.</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7009,12 +7017,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>0.0009782</t>
+          <t>0.0008015</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>0.04106645</t>
+          <t>0.04088975</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr"/>
@@ -7101,7 +7109,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
@@ -7111,7 +7119,7 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>Coincidencia completa: la respuesta real lista 27 perfiles que coinciden con los esperados.</t>
+          <t>Lista de 27 perfiles coincide con la esperada; responde directamente sobre japonés o ruso.</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -7121,12 +7129,12 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>0.0009782</t>
+          <t>0.0008015</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>0.0430152</t>
+          <t>0.0428385</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr"/>
@@ -7197,7 +7205,7 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>95</t>
         </is>
       </c>
       <c r="L67" s="3" t="inlineStr">
@@ -7207,7 +7215,7 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>Coincidencia completa: los 6 candidatos esperados aparecen en la lista principal de la respuesta real.</t>
+          <t>Incluye todos los candidatos esperados y algunos adicionales con skills relevantes; responde bien a la pregunta de iOS/Android.</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -7217,12 +7225,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>0.0009782</t>
+          <t>0.0008015</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>0.06867995</t>
+          <t>0.06850325</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr"/>
@@ -7288,17 +7296,17 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="L68" s="4" t="inlineStr">
+          <t>75</t>
+        </is>
+      </c>
+      <c r="L68" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>La real incluye 3/5 esperados (Nancy, Liam, Arjun) pero omite a Bruce O'Connor O'Brien y Ming Bell Rose; añade extra formación no solicitada.</t>
+          <t>Aparecen 3 de 5 esperados; añade perfiles con formación en web (algunos no son puestos actuales), respuesta parcial y algo ruidosa.</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -7308,12 +7316,12 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>0.0009782</t>
+          <t>0.0008015</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>0.07191445</t>
+          <t>0.07173775</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr"/>
@@ -7373,7 +7381,7 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -7383,7 +7391,7 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>Solo 1/5 esperados aparece (William Freeman Allen); faltan Alice Flores Adeyemi, Chen Phillips Mensah, Evelyn Tran Morgan, Rohan Sanders Ashworth.</t>
+          <t>Solo devuelve 1 de 5 arquitectos/lead esperados (William Freeman Allen); omite varios nombres esperados, respuesta incompleta.</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -7393,12 +7401,12 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>0.0009782</t>
+          <t>0.0008015</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>0.0565847</t>
+          <t>0.056408</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr"/>
@@ -7452,7 +7460,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
@@ -7462,7 +7470,7 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>No hay respuesta real proporcionada para esta pregunta (vacío), por tanto no coincide con la lista esperada.</t>
+          <t>No hay respuesta real proporcionada; no cubre la lista esperada ni responde a la pregunta sobre microservicios/Kafka.</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -7472,12 +7480,12 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>0.0009782</t>
+          <t>0.0008015</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>0.04094695</t>
+          <t>0.04077025</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr"/>
@@ -7687,12 +7695,12 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>85</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>90</t>
         </is>
       </c>
       <c r="L71" s="3" t="inlineStr">
@@ -7702,7 +7710,7 @@
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>La real devuelve 155 perfiles e incluye la mayoría de los esperados y muchos adicionales (BERT y experiencia en datos); faltas menores posibles.</t>
+          <t>Respuesta muy amplia (155 perfiles) que cubre la mayoría de las entidades esperadas y menciona BERT/experiencia en datos; algo ruidosa pero pertinente.</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -7712,12 +7720,12 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>0.0009782</t>
+          <t>0.0008015</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>0.0449692</t>
+          <t>0.0447925</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr"/>
@@ -7922,12 +7930,12 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>85</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>95</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
@@ -7937,7 +7945,7 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>La respuesta real incluye la mayoría (≈24/28) de los nombres esperados (Andrei, Arjun, Ashley, Beverly, etc.), faltan pocos (p.ej. Colton, Frank, Parker Davis Jackson, Austin).</t>
+          <t>Incluye la mayoría de nombres esperados (Priya, Spencer, Mason, etc.), pero omite algunos como Colton o Parker.</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -7947,12 +7955,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>0.00153295</t>
+          <t>0.00125225</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>0.0517222</t>
+          <t>0.0514415</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr"/>
@@ -8170,7 +8178,7 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L73" s="3" t="inlineStr">
@@ -8180,7 +8188,7 @@
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>La respuesta real contiene todos los nombres esperados (las 16 entidades solicitadas aparecen explícitamente en la lista).</t>
+          <t>Incluye todos los nombres esperados; responde directamente con perfiles relevantes.</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -8190,12 +8198,12 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>0.00153295</t>
+          <t>0.00125225</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>0.05027195</t>
+          <t>0.04999125</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr"/>
@@ -8295,7 +8303,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
@@ -8305,7 +8313,7 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>La respuesta real incluye todos los nombres esperados relacionados con microservicios (todas las entidades del gold aparecen).</t>
+          <t>Incluye todos los esperados relacionados con microservicios; respuesta clara y completa.</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -8315,12 +8323,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>0.00153295</t>
+          <t>0.00125225</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>0.06247445</t>
+          <t>0.06219375</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr"/>
@@ -8445,17 +8453,17 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="L75" s="5" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L75" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>La respuesta real cubre una buena parte de los 41 esperados (muchos nombres clave aparecen), pero omite o no muestra claramente varios candidatos del gold. Cobertura parcial.</t>
+          <t>Cubre muchos perfiles de datos esperados pero omite varios (p.ej. Alan Lynch Lane, Alexis Jenkins Burns, Patrick Maddox Volkov).</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -8465,12 +8473,12 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>0.00153295</t>
+          <t>0.00125225</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>0.0962672</t>
+          <t>0.0959865</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr"/>
@@ -8601,12 +8609,12 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>90</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>95</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
@@ -8616,7 +8624,7 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>La respuesta real incluye todos los 25 nombres esperados relacionados con cloud; la mayoría aparecen explícitamente en la lista extensa proporcionada.</t>
+          <t>Incluye casi todos los perfiles cloud esperados (p.ej. Arjun, Priya, Mason), aunque lista muchos adicionales; responde directamente.</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -8626,12 +8634,12 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>0.00153295</t>
+          <t>0.00125225</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>0.0755647</t>
+          <t>0.075284</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr"/>
@@ -8756,7 +8764,7 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L77" s="3" t="inlineStr">
@@ -8766,7 +8774,7 @@
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>La respuesta real contiene todos los 13 candidatos esperados con experiencia en DevOps (todos los nombres del gold están presentes).</t>
+          <t>Incluye todos los nombres esperados de DevOps y amplia la lista; responde directamente.</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -8776,12 +8784,12 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>0.00153295</t>
+          <t>0.00125225</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>0.0980617</t>
+          <t>0.097781</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr"/>
@@ -8971,17 +8979,17 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="L78" s="4" t="inlineStr">
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L78" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>La esperada es 300 CVs pero la real reporta 130 perfiles: cobertura claramente insuficiente (~43%).</t>
+          <t>Devuelve 130 CVs explícitos en lugar de 300 esperados; responde numéricamente pero difiere del valor esperado.</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -8991,12 +8999,12 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>0.00153295</t>
+          <t>0.00125225</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>0.0983002</t>
+          <t>0.0980195</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr"/>
@@ -9144,22 +9152,22 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="L79" s="4" t="inlineStr">
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L79" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>Se esperaban 169 posiciones distintas; la real devuelve 94 en su recuento —aprox. 55–56% de la cifra esperada (cobertura parcial).</t>
+          <t>Devuelve 94 posiciones distintas listadas, menos que las 169 esperadas; contesta la pregunta pero subestima el total.</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9169,12 +9177,12 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>0.00153295</t>
+          <t>0.00125225</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>0.0906482</t>
+          <t>0.0903675</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr"/>
@@ -9232,12 +9240,12 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>30</t>
         </is>
       </c>
       <c r="L80" s="4" t="inlineStr">
@@ -9247,7 +9255,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>Se esperaban 639 hard skills distintos; la respuesta real solo muestra 3 perfiles con conteos parciales, sin sumar el total: cobertura prácticamente nula.</t>
+          <t>Solo lista 3 perfiles con conteos por CV; no proporciona el total de habilidades distintas requerido (esperado 639).</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9257,12 +9265,12 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>0.00153295</t>
+          <t>0.00125225</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>0.09405545</t>
+          <t>0.09377475</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr"/>
@@ -9400,22 +9408,22 @@
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="L81" s="5" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>Se esperaban 121 candidatos ≥8 hard skills; la real lista 84 perfiles (≈69% de la expectativa), es una cobertura moderada pero incompleta.</t>
+          <t>Lista 84 candidatos con ≥8 hard skills (menos que 121 esperado); responde la consulta pero subcuenta.</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -9425,12 +9433,12 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>0.00153295</t>
+          <t>0.00125225</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>0.08328945</t>
+          <t>0.08300875</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr"/>
@@ -9488,22 +9496,22 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="L82" s="4" t="inlineStr">
+          <t>80</t>
+        </is>
+      </c>
+      <c r="L82" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>Reporta 3 perfiles vs 6 esperados; falta la mitad de los candidatos, omisión significativa.</t>
+          <t>Esperado 6 pero la respuesta da 3 perfiles (faltan 3). Contenido es pertinente pero incompleto respecto al recuento.</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -9513,12 +9521,12 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>0.0005772</t>
+          <t>0.00070525</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>0.03168145</t>
+          <t>0.0318095</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr"/>
@@ -9677,17 +9685,17 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="L83" s="5" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>Reporta 99 perfiles vs 104 esperados; solo 5 ausentes, coincide en la gran mayoría.</t>
+          <t>Esperado 104, la respuesta lista 99 (faltan 5). Cubre la gran mayoría de entidades y es pertinente a la pregunta.</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -9697,12 +9705,12 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>0.0005772</t>
+          <t>0.00070525</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>0.0389477</t>
+          <t>0.03907575</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr"/>
@@ -9771,17 +9779,17 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="L84" s="5" t="inlineStr">
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>Reporta 9 perfiles exactamente como se esperaba (9/9), coincidencia total.</t>
+          <t>Coincide exactamente: esperado 9 y respuesta muestra 9 perfiles con Django o Flask. Respuesta completa y directa.</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -9791,12 +9799,12 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>0.0005772</t>
+          <t>0.00070525</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>0.0433022</t>
+          <t>0.04343025</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr"/>
@@ -9969,22 +9977,22 @@
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>90</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="L85" s="5" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>Reporta 118 perfiles vs 129 esperados; faltan 11 perfiles (~8.5%), coincide en la mayoría.</t>
+          <t>Esperado 129, la respuesta da 118 (faltan 11). Muy cercana y relevante, aunque omite varios perfiles.</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -9994,12 +10002,12 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>0.0005772</t>
+          <t>0.00070525</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>0.0848887</t>
+          <t>0.08501675</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr"/>
@@ -10089,22 +10097,22 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>90</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="L86" s="5" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>Reporta 35 perfiles vs 38 esperados; faltan 3 perfiles (~8%), cubre la mayoría.</t>
+          <t>Esperado 38, la respuesta lista 35 (faltan 3). Cubre la mayoría y responde directamente.</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -10114,12 +10122,12 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>0.0005772</t>
+          <t>0.00070525</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>0.05437095</t>
+          <t>0.054499</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr"/>
@@ -10276,7 +10284,7 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>50</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
@@ -10286,7 +10294,7 @@
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>Reporta 97 perfiles vs 52 esperados; sobreestima por 45 perfiles e incluye elementos probablemente irrelevantes.</t>
+          <t>Esperado 52 pero la respuesta da 97 (sobreconteo grande). Está en tema (microservices/cloud) pero contiene muchos errores/duplicados.</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -10296,12 +10304,12 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>0.0005772</t>
+          <t>0.00070525</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>0.0641487</t>
+          <t>0.06427675</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr"/>
@@ -10494,17 +10502,17 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L2" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>6 de 9 nombres esperados aparecen (Ariana, Montserrat, Omar M., Omar S., Pablo, Ricardo Molina). Faltan Mercè Varela, Ricardo Bosch y Ruth; incluye 1 extra (Inés).</t>
+          <t>Incluye 6/9 esperados; añade Inés (ELK como proxy de Elasticsearch) y omite Mercè Varela, Ricardo Bosch y Ruth Domínguez.</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -10514,12 +10522,12 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>0.0005532</t>
+          <t>0.000637</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>0.0058767</t>
+          <t>0.0059605</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr"/>
@@ -10586,17 +10594,17 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
+          <t>80</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>4 de 9 nombres esperados aparecen (Fabián, Mateo, Rosa, Mercè Espinosa). Faltan Alex, Eric, Nieves, Raúl y Sonia.</t>
+          <t>Incluye 4/9 esperados (Fabián, Mateo, Rosa, Mercè). Respuesta directa y coherente pero incompleta respecto al listado esperado.</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -10606,12 +10614,12 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>0.0005532</t>
+          <t>0.000637</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>0.0038922</t>
+          <t>0.003976</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr"/>
@@ -10674,7 +10682,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
@@ -10684,7 +10692,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2 de 8 nombres esperados aparecen (Paloma Rojas, Silvia Palomo). Omite 6 candidatos clave del listado esperado.</t>
+          <t>Solo 2/8 esperados (Paloma, Silvia). Respuesta es directa pero muy incompleta respecto a la lista esperada.</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10694,12 +10702,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0.0005532</t>
+          <t>0.000637</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0.00300795</t>
+          <t>0.00309175</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr"/>
@@ -10768,17 +10776,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5 de 8 nombres esperados aparecen (Tatiana, Khadija, Susana, Daniel, Joaquín). Faltan Ismael, Joel Hermida y Mateo Salas.</t>
+          <t>Cubre 5/8 esperados (Tatiana, Khadija, Susana, Daniel, Joaquín). Respuesta coherente y pertinente aunque no exhaustiva.</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10788,12 +10796,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0.0005532</t>
+          <t>0.000637</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0.0038707</t>
+          <t>0.0039545</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr"/>
@@ -10862,17 +10870,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
+          <t>85</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5 de 9 nombres esperados aparecen (Tomás, Joaquín Vilar, Maximiliano, Inmaculada, José Javier). Faltan Helena, Joel Calvo, José De la Torre y Martina.</t>
+          <t>Cubre 5/9 esperados (Tomás, Joaquín V., Maximiliano, Inmaculada, José J.). Respuesta clara pero faltan varios nombres esperados.</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10882,12 +10890,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0.0005532</t>
+          <t>0.000637</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0.0041377</t>
+          <t>0.0042215</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr"/>
@@ -10956,7 +10964,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -10966,7 +10974,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Todos los 5 nombres esperados aparecen (Sofía, Abril, Chen, Margarita, Ruth). Cobertura completa.</t>
+          <t>Cubre exactamente los 5 esperados (Abril, Chen, Margarita, Ruth, Sofía). Coincidencia y pertinencia completas.</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10976,12 +10984,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0.0005532</t>
+          <t>0.000637</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0.0037587</t>
+          <t>0.0038425</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr"/>
@@ -11050,17 +11058,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5 de 7 nombres esperados aparecen (Francisco, Ramón, Eugenio, Youssef, Octavio). Faltan Abril Santillana y Marina Santamaría.</t>
+          <t>Cubre 5/7 esperados (Francisco, Ramón, Eugenio, Youssef, Octavio). Respuesta relevante y coherente aunque no exhaustiva.</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11070,12 +11078,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0.0005532</t>
+          <t>0.000637</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0.00430645</t>
+          <t>0.00439025</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr"/>
@@ -11142,17 +11150,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4 de 7 nombres esperados aparecen (Eva Santiago, Alex Cervantes, Mateo Salas, Ana María Rivas). Faltan Jorge, María Luisa y Rodrigo.</t>
+          <t>Cubre 4/7 esperados (Eva, Alex, Mateo, Ana María). Respuesta correcta y pertinente pero omite algunos candidatos.</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11162,12 +11170,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0.0005532</t>
+          <t>0.000637</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0.00443545</t>
+          <t>0.00451925</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr"/>
@@ -11232,7 +11240,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -11242,7 +11250,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Los 3 nombres esperados aparecen (Gustavo Montes, Joel Azkue, Omar Cervantes). Cobertura completa.</t>
+          <t>Cubre exactamente los 3 esperados (Joel Azkue, Gustavo Montes, Omar Cervantes). Respuesta precisa y completa.</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11252,12 +11260,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0.0005532</t>
+          <t>0.000637</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0.00373145</t>
+          <t>0.00381525</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr"/>
@@ -11322,7 +11330,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -11332,7 +11340,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Los 3 nombres esperados aparecen (Alex Santa Cruz, Begoña Gómez, Marina Granados). Cobertura completa.</t>
+          <t>Cubre exactamente los 3 esperados (Alex Santa Cruz, Begoña Gómez, Marina Granados). Respuesta precisa y completa.</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11342,12 +11350,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0.0005532</t>
+          <t>0.000637</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0.00361645</t>
+          <t>0.00370025</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr"/>
@@ -11410,7 +11418,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -11420,7 +11428,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Ambos nombres esperados aparecen en la respuesta real.</t>
+          <t>Lista exactamente las dos personas esperadas (Noah De los Santos Herrera y Sofía Linares Urbano) y responde directamente la pregunta.</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11430,12 +11438,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0.0013682</t>
+          <t>0.000682</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0.00389145</t>
+          <t>0.00320525</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr"/>
@@ -11500,7 +11508,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -11510,7 +11518,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Los tres nombres esperados aparecen en la respuesta real.</t>
+          <t>Incluye los tres nombres esperados (Alberto, David y Fabián) con detalles; respuesta completa y pertinente.</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11520,12 +11528,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0.0013682</t>
+          <t>0.000682</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0.00453945</t>
+          <t>0.00385325</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr"/>
@@ -11588,7 +11596,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -11598,7 +11606,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Ambos nombres esperados aparecen en la respuesta real.</t>
+          <t>Contiene ambos registros esperados (José Ángel Vila Pascual y Li San Miguel Rivero); responde exactamente a la pregunta.</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11608,12 +11616,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0.0013682</t>
+          <t>0.000682</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0.00449345</t>
+          <t>0.00380725</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr"/>
@@ -11676,7 +11684,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -11686,7 +11694,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Ambos nombres esperados aparecen en la respuesta real.</t>
+          <t>Incluye los dos candidatos esperados (Izan Lozano Recio y Jorge Durán Barrios); respuesta completa y directa.</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11696,12 +11704,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0.0013682</t>
+          <t>0.000682</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0.00387895</t>
+          <t>0.00319275</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr"/>
@@ -11788,17 +11796,17 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="L16" s="4" t="inlineStr">
+          <t>70</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Se encontraron 14 de 58 nombres esperados (≈24%), omite la mayoría de los profesionales listados.</t>
+          <t>Lista 14 perfiles con francés, muchos coinciden con el gold pero falta gran parte del listado esperado; responde a la pregunta aunque incompleta.</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11808,12 +11816,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0.0013682</t>
+          <t>0.000682</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0.0060167</t>
+          <t>0.0053305</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr"/>
@@ -11907,17 +11915,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
+          <t>75</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Se encontraron 17 de 68 nombres esperados (≈25%), omite la mayoría de los profesionales listados.</t>
+          <t>Proporciona 17 perfiles con alemán, incluye varios esperados pero omite muchos otros del gold; respuesta pertinente pero parcial.</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11927,12 +11935,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0.0013682</t>
+          <t>0.000682</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0.0073387</t>
+          <t>0.0066525</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr"/>
@@ -12006,22 +12014,22 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
+          <t>85</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Se encontraron 10 de 20 nombres esperados (50%), cobertura parcial de la lista esperada.</t>
+          <t>Encuentra 10 profesionales con italiano, varios coinciden con el gold (aprox mitad); responde bien pero no cubre todo el listado esperado.</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12031,12 +12039,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0.0013682</t>
+          <t>0.000682</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>0.00601095</t>
+          <t>0.00532475</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr"/>
@@ -12104,22 +12112,22 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>KO</t>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Se encontraron 7 de 11 nombres esperados (≈64%), faltan 4 profesionales esperados.</t>
+          <t>Reporta 7 perfiles con portugués, la mayoría aparecen en la lista esperada pero faltan varios nombres; respuesta relevante y directa.</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12129,12 +12137,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0.0013682</t>
+          <t>0.000682</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0.0052152</t>
+          <t>0.004529</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr"/>
@@ -12214,12 +12222,12 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>75</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>85</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
@@ -12229,7 +12237,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Se encontraron 13 de 17 nombres esperados (≈76%), cubre la mayoría pero faltan algunos.</t>
+          <t>Listado de 13 candidatos con japonés, cubre la mayor parte del gold (faltan algunos). Responde claramente a la pregunta.</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12239,12 +12247,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0.0013682</t>
+          <t>0.000682</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0.0070222</t>
+          <t>0.006336</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr"/>
@@ -12323,7 +12331,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
@@ -12333,7 +12341,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Los 10 nombres esperados aparecen en la respuesta real.</t>
+          <t>Incluye exactamente los diez candidatos esperados con experiencia en startups; respuesta completa y directamente relevante.</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12343,12 +12351,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0.0013682</t>
+          <t>0.000682</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0.00702245</t>
+          <t>0.00633625</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr"/>
@@ -12431,17 +12439,17 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
+          <t>85</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>Incluye 12 de 21 candidatos esperados (12/21). Cubre muchos casos pero omite varios nombres clave del listado esperado.</t>
+          <t>Incluye 12 de 21 candidatos esperados; omite varios nombres del gold pero lista perfiles relevantes que mencionan trabajo remoto.</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12451,12 +12459,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0.00058095</t>
+          <t>0.000795</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0.0056342</t>
+          <t>0.00584825</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr"/>
@@ -12541,17 +12549,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
+          <t>85</t>
+        </is>
+      </c>
+      <c r="L23" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>Incluye 13 de 19 candidatos esperados (13/19). Buena cobertura pero faltan varios candidatos del gold standard.</t>
+          <t>Cubre 13 de 19 nombres esperados; faltan varios candidatos, pero la respuesta identifica correctamente múltiples contribuyentes open source.</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12561,12 +12569,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0.00058095</t>
+          <t>0.000795</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0.00485495</t>
+          <t>0.005069</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr"/>
@@ -12633,7 +12641,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
@@ -12643,7 +12651,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>Solo 4 de 12 esperados (4/12). Coincidencia parcial limitada; omite la mayoría de los candidatos listados.</t>
+          <t>Solo 4 de 12 candidatos esperados aparecen. La respuesta es pertinente pero claramente incompleta frente al gold.</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12653,12 +12661,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0.00058095</t>
+          <t>0.000795</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0.00382145</t>
+          <t>0.0040355</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr"/>
@@ -12726,22 +12734,22 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7 de 22 esperados (7/22). Cobertura baja: aparecen algunos mentores pero faltan muchos nombres del estándar.</t>
+          <t>Incluye 7 de 22 nombres esperados. Responde directamente sobre mentoría, pero omite muchos perfiles listados en el gold.</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12751,12 +12759,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0.00058095</t>
+          <t>0.000795</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0.0057072</t>
+          <t>0.00592125</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr"/>
@@ -12835,7 +12843,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>90</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
@@ -12845,7 +12853,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>Incluye 10 de 12 esperados (10/12). Cubre la gran mayoría de los candidatos esperados con pequeñas omisiones.</t>
+          <t>Lista 10 de 12 esperados (faltan Ainhoa y Ana María). Cubre la gran mayoría y responde de forma directa y pertinente.</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12855,12 +12863,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0.00058095</t>
+          <t>0.000795</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0.0055177</t>
+          <t>0.00573175</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr"/>
@@ -12927,7 +12935,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
@@ -12937,7 +12945,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>Incluye exactamente los 4 candidatos esperados (4/4) con las dos condiciones (francés y microservicios). Completa.</t>
+          <t>Coincide exactamente con los 4 nombres del gold; respuesta completa y plenamente pertinente a la pregunta.</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12947,12 +12955,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0.00058095</t>
+          <t>0.000795</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>0.0048912</t>
+          <t>0.00510525</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr"/>
@@ -13015,17 +13023,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="L28" s="5" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L28" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>Incluye 2 de 3 esperados (2/3). Cubre la mayoría pero falta Fátima Escobar Ferreiro del listado esperado.</t>
+          <t>Incluye 2 de 3 esperados (falta Fátima Escobar). Responde de forma clara y relevante aunque no completa respecto al gold.</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13035,12 +13043,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0.00058095</t>
+          <t>0.000795</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0.0050232</t>
+          <t>0.00523725</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr"/>
@@ -13105,7 +13113,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
@@ -13115,7 +13123,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>El candidato esperado (Emilio Matas Durán) aparece; aunque añade otros, cubre toda la información requerida.</t>
+          <t>Contiene al candidato esperado y añade dos más; cubre totalmente el gold y aporta información adicional relevante.</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13125,12 +13133,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0.00058095</t>
+          <t>0.000795</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0.00401995</t>
+          <t>0.004234</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr"/>
@@ -13191,17 +13199,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>No aparece la persona esperada (Rosa María Villar Delgado); el resultado muestra un candidato distinto, sin coincidencias.</t>
+          <t>No incluye a la persona esperada (Rosa María Villar Delgado) pero aporta un candidato válido que cumple portugués y metodologías ágiles.</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13211,12 +13219,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0.00058095</t>
+          <t>0.000795</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0.00445945</t>
+          <t>0.0046735</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr"/>
@@ -13279,17 +13287,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="L31" s="5" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L31" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>Incluye 2 de 3 esperados (Elena y José Ángel) pero omite a Liam Elizondo Martínez; cobertura parcial (2/3).</t>
+          <t>Incluye 2 de 3 esperados (faltó Liam Elizondo Martínez). Responde directamente y es pertinente, aunque no totalmente completo.</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13299,12 +13307,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0.00058095</t>
+          <t>0.000795</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0.00526845</t>
+          <t>0.0054825</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr"/>
@@ -13360,22 +13368,22 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>Devuelve Hugo Martín Ribas en lugar de Simón Masip Sandoval; el candidato esperado no aparece.</t>
+          <t>Responde al criterio (encuentra un perfil con startups y cloud) pero identifica a Hugo Martín Ribas en vez de Simón Masip Sandoval; omite el candidato esperado.</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13385,12 +13393,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0.0004457</t>
+          <t>0.00045975</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0.0039577</t>
+          <t>0.00397175</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr"/>
@@ -13466,17 +13474,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="L33" s="5" t="inlineStr">
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>Coincide: la respuesta real indica correctamente que no hay perfiles que cumplan ambos criterios.</t>
+          <t>Coincide con la respuesta esperada (ningún perfil cumple ambos criterios). Respuesta clara y ofrece sugerencias prácticas para ampliar la búsqueda.</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -13486,12 +13494,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0.0004457</t>
+          <t>0.00045975</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>0.0093462</t>
+          <t>0.00936025</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr"/>
@@ -13556,17 +13564,17 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>Incluye 3 de 5 esperados (José Ángel Bosch, José De la Torre, Marina); faltan Helena Ramos y Martina Llopis.</t>
+          <t>Encuentra 3 de los 5 esperados (José Ángel Bosch, José De la Torre, Marina García). Faltan Helena Ramos Sanz y Martina Llopis Zamorano.</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -13576,12 +13584,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0.0004457</t>
+          <t>0.00045975</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0.0058052</t>
+          <t>0.00581925</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr"/>
@@ -13644,7 +13652,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>95</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
@@ -13654,7 +13662,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>Incluye al candidato esperado Mateo Murillo Zamorano (además añade otro perfil adicional).</t>
+          <t>Incluye al candidato esperado (Mateo Murillo Zamorano) y aporta un candidato adicional relevante. Responde directamente a la pregunta.</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -13664,12 +13672,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0.0004457</t>
+          <t>0.00045975</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>0.0046987</t>
+          <t>0.00471275</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr"/>
@@ -13734,17 +13742,17 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="L36" s="4" t="inlineStr">
+          <t>85</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>Incluye 3 de 5 esperados (Joaquín Vilar, José Ramón Castro, Salvador Castillo); faltan José De la Torre y José Ángel Bosch.</t>
+          <t>Devuelve 3 de los 5 esperados (Joaquín Vilar, José Ramón Castro, Salvador Castillo); faltan José De la Torre y José Ángel Bosch.</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13754,12 +13762,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0.0004457</t>
+          <t>0.00045975</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0.0044612</t>
+          <t>0.00447525</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr"/>
@@ -13820,7 +13828,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
@@ -13830,7 +13838,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>Incluye al candidato esperado Héctor Ibáñez Castro y coincide con la respuesta esperada.</t>
+          <t>Incluye exactamente al candidato esperado (Héctor Ibáñez Castro); respuesta directa y precisa.</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13840,12 +13848,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0.0004457</t>
+          <t>0.00045975</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>0.0043447</t>
+          <t>0.00435875</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr"/>
@@ -13906,7 +13914,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -13916,7 +13924,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>Incluye al candidato esperado José Urbano Gil y coincide con la respuesta esperada.</t>
+          <t>Incluye exactamente al candidato esperado (José Urbano Gil); respuesta clara y pertinente.</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13926,12 +13934,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0.0004457</t>
+          <t>0.00045975</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>0.0035672</t>
+          <t>0.00358125</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr"/>
@@ -13994,17 +14002,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="L39" s="5" t="inlineStr">
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>Coincide: la respuesta real indica correctamente que no hay perfiles que cumplan ambos criterios.</t>
+          <t>Coincide con la respuesta esperada (ningún perfil cumple ambos criterios) y ofrece vías para verificar y ampliar la búsqueda.</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -14014,12 +14022,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0.0004457</t>
+          <t>0.00045975</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>0.00426495</t>
+          <t>0.004279</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr"/>
@@ -14085,17 +14093,17 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="L40" s="5" t="inlineStr">
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>Coincide: la respuesta real indica correctamente que no hay perfiles que cumplan ambos criterios.</t>
+          <t>Coincide con la respuesta esperada (ningún perfil cumple simultáneamente startups y hackathones); incluye sugerencias operativas.</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14105,12 +14113,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0.0004457</t>
+          <t>0.00045975</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>0.0053812</t>
+          <t>0.00539525</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr"/>
@@ -14198,17 +14206,17 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="L41" s="5" t="inlineStr">
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>Coincide: la respuesta real indica correctamente que no hay perfiles que cumplan ambos criterios.</t>
+          <t>Coincide con la respuesta esperada (ningún perfil cumple trabajo remoto y open source) y proporciona listas útiles para cruce y verificación.</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -14218,12 +14226,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0.0004457</t>
+          <t>0.00045975</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>0.0068127</t>
+          <t>0.00682675</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr"/>
@@ -14299,22 +14307,22 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
+          <t>80</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>Respuesta real niega coincidencias pero menciona a Jorge en alternativas sin afirmar fintech+banca simultáneo; expected era Jorge. Omite confirmación clave.</t>
+          <t>Declara 0 perfiles con fintech+y banca (contradice el esperado). Sugiere candidatos pero omite el resultado esperado concreto.</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -14324,12 +14332,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0.0012122</t>
+          <t>0.00080025</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>0.0074892</t>
+          <t>0.00707725</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr"/>
@@ -14397,22 +14405,22 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="L43" s="4" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>Expected 15 nombres; la respuesta real lista 7 (Amine, Carlos, Fatima, Guillermo, Juan José, Verónica, Youssef), cubre ~7/15, falta el resto.</t>
+          <t>Lista 7 de 14 esperados (Fatima, Verónica, Juan José, Amine, Carlos, Youssef, Guillermo); faltan varios nombres.</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -14422,12 +14430,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0.0012122</t>
+          <t>0.00080025</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>0.0059642</t>
+          <t>0.00555225</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr"/>
@@ -14492,17 +14500,17 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="L44" s="4" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>Expected 5 nombres; la respuesta real incluye 3 (Gustavo, Sonia, Octavio) → 3/5 coinciden, cubre la mayoría pero no todos.</t>
+          <t>Cubre 3/5 esperados (Gustavo, Sonia, Octavio). Omite Alex Cervantes y Emilio Matas.</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -14512,12 +14520,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0.0012122</t>
+          <t>0.00080025</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>0.00478295</t>
+          <t>0.004371</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr"/>
@@ -14602,17 +14610,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="L45" s="5" t="inlineStr">
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>Expected vacío y la respuesta real también indica que no hay perfiles con microservicios Y cloud; coincidencia total.</t>
+          <t>Coincide con la respuesta esperada: no hay perfiles con microservicios Y cloud; ofrece alternativas útiles.</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -14622,12 +14630,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>0.0012122</t>
+          <t>0.00080025</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>0.00956695</t>
+          <t>0.009155</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr"/>
@@ -14702,17 +14710,17 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="L46" s="5" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L46" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>Expected 3 nombres; la respuesta real incluye 2 (Begoña, Daniel) de los 3 y añade otros 6 perfiles relevantes → cobertura parcial.</t>
+          <t>Incluye 8 perfiles y cubre a Begoña y Daniel pero omite a Eugenio Santiago Franco; cobertura parcial.</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -14722,12 +14730,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0.0012122</t>
+          <t>0.00080025</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>0.00886745</t>
+          <t>0.0084555</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr"/>
@@ -14790,17 +14798,17 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="L47" s="4" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>Expected Joaquín y Natalia; la respuesta real incluye a Joaquín Ortega pero no a Natalia Molina → cubre la mitad del esperado.</t>
+          <t>Encuentra 2 perfiles (Lucía y Joaquín); coincide con Joaquín pero no con Natalia Molina, cobertura parcial.</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -14810,12 +14818,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0.0012122</t>
+          <t>0.00080025</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>0.00631345</t>
+          <t>0.0059015</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr"/>
@@ -14898,17 +14906,17 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="L48" s="4" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>Expected 65 nombres; la real lista 12 y todos están en la lista esperada, pero cubre solo 12/65 (~18-20%), por tanto baja coincidencia.</t>
+          <t>Lista 12 candidatos que cumplen francés O microservices, todos están en el esperado pero representan ~20% de la lista esperada.</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -14918,12 +14926,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0.0012122</t>
+          <t>0.00080025</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>0.0075447</t>
+          <t>0.00713275</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr"/>
@@ -15009,17 +15017,17 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="L49" s="4" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>Expected 76 nombres; la respuesta real lista 13 (todos dentro del esperado) pero representa solo ~17% de la lista esperada, coincidencia baja.</t>
+          <t>Devuelve 13 perfiles (todos por alemán) y señala que no halló Kafka; coincide parcialmente con el gran listado esperado.</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -15029,12 +15037,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0.0012122</t>
+          <t>0.00080025</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>0.0072967</t>
+          <t>0.00688475</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr"/>
@@ -15106,17 +15114,17 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="L50" s="4" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>Expected 26 nombres; la real lista 6 (José Urbano, Octavio, Gustavo, Abril, Wang, Elena) → ~6/26 ≈25% de coincidencia.</t>
+          <t>Encuentra 6 perfiles (todos esperados) por italiano; no halló Django. Cobertura limitada respecto al listado esperado.</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -15126,12 +15134,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0.0012122</t>
+          <t>0.00080025</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>0.00553895</t>
+          <t>0.005127</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr"/>
@@ -15195,22 +15203,22 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="L51" s="4" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>Expected 20 nombres; la respuesta real incluye 5 coincidentes (Montserrat, Marta, Salvador, Nicolás, Eric) → 5/20 = 25% de cobertura.</t>
+          <t>Incluye 5 perfiles esperados (portugués o Elasticsearch); responde a la pregunta pero cubre solo parte de la lista esperada.</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -15220,12 +15228,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>0.0012122</t>
+          <t>0.00080025</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>0.00469345</t>
+          <t>0.0042815</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr"/>
@@ -15308,17 +15316,17 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="L52" s="4" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>Encontró 12 de 24 nombres esperados (50%). Cubre la mitad, faltan 12 candidatos del gold.</t>
+          <t>Incluye 12 de 24 esperados (≈50%), cubre correctamente la intención (japonés o OpenCV) pero omite muchos nombres del gold.</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -15328,12 +15336,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0.0009772</t>
+          <t>0.00077325</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>0.00714045</t>
+          <t>0.0069365</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr"/>
@@ -15401,22 +15409,22 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="L53" s="4" t="inlineStr">
+          <t>85</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>Encontró 7 de 12 nombres esperados (58%). Faltan 5 candidatos del gold.</t>
+          <t>Aporta 7 de 12 esperados (~50%). Responde de forma pertinente al requisito (ruso o BERT) pero falta cobertura de varios candidatos.</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -15426,12 +15434,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0.0009772</t>
+          <t>0.00077325</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>0.00499445</t>
+          <t>0.0047905</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr"/>
@@ -15501,22 +15509,22 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="L54" s="4" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L54" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>Encontró 8 de 14 nombres esperados (57%). Omite varios candidatos esperados.</t>
+          <t>Lista 8 de 14 esperados (~57%). Responde directamente (árabe o Flask) y acierta varios nombres, pese a omisiones notables.</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -15526,12 +15534,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>0.0009772</t>
+          <t>0.00077325</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>0.00722245</t>
+          <t>0.0070185</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr"/>
@@ -15607,22 +15615,22 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="L55" s="4" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>Encontró 10 de 17 nombres esperados (59%). Cubre muchos pero falta un número significativo.</t>
+          <t>Incluye 11 de 17 esperados (~65% overlap). Responde bien a Microservices o Kafka, pero faltan varios candidatos del gold.</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -15632,12 +15640,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0.0009772</t>
+          <t>0.00077325</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>0.00656795</t>
+          <t>0.006364</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr"/>
@@ -15720,7 +15728,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
@@ -15730,7 +15738,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>Cubre exactamente los 12 candidatos esperados (100%).</t>
+          <t>Cubre todos los candidatos esperados (12/12). Respuesta completa y directamente relevante a Django o Flask.</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -15740,12 +15748,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0.0009772</t>
+          <t>0.00077325</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>0.00677945</t>
+          <t>0.0065755</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr"/>
@@ -15829,12 +15837,12 @@
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>85</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>95</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
@@ -15844,7 +15852,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>Encontró 12 de 13 nombres esperados (92%). Solo falta Enrique Cruz Rivero del gold.</t>
+          <t>Incluye la mayoría de los esperados (≈11/13) y añade perfiles extra; muy relevante y con buena cobertura.</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -15854,12 +15862,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>0.0009772</t>
+          <t>0.00077325</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>0.00569295</t>
+          <t>0.005489</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr"/>
@@ -15933,12 +15941,12 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>85</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>95</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
@@ -15948,7 +15956,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>Encontró 10 de 12 nombres esperados (83%). Faltan Ismael Medina López y Mateo Camacho Pereira.</t>
+          <t>Cubre 10 de 12 esperados (~83%). Respuesta clara y pertinente sobre OpenCV o BERT, con pocas ausencias.</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -15958,12 +15966,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>0.0009772</t>
+          <t>0.00077325</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>0.00672995</t>
+          <t>0.006526</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr"/>
@@ -16037,12 +16045,12 @@
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>90</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
@@ -16052,7 +16060,7 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>Encontró 10 de 13 nombres esperados (77%). Omite 3 candidatos (dos 'Abril' y Marina Santamaría).</t>
+          <t>Lista 10 de 13 esperados (~77%). Responde bien a Airflow o Glue, aunque faltan algunos nombres del gold.</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -16062,12 +16070,12 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>0.0009772</t>
+          <t>0.00077325</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>0.0057597</t>
+          <t>0.00555575</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr"/>
@@ -16145,12 +16153,12 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>90</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>95</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
@@ -16160,7 +16168,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>Encontró 12 de 13 nombres esperados (92%). Solo falta Alberto Valls Montoya.</t>
+          <t>Muy cercana al gold (≈12/13). Responde directamente a WebSockets o gRPC y cubre casi todos los candidatos esperados.</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -16170,12 +16178,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>0.0009772</t>
+          <t>0.00077325</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>0.00696245</t>
+          <t>0.0067585</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr"/>
@@ -16247,22 +16255,22 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="L61" s="4" t="inlineStr">
+          <t>80</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>Encontró 9 de 23 nombres esperados (39%). Cubre pocos; faltan muchos candidatos del gold.</t>
+          <t>Solo 9 perfiles listados frente a 23 esperados (~39%); la respuesta es relevante (startups/hackathons) pero con cobertura muy limitada.</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -16272,12 +16280,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>0.0009772</t>
+          <t>0.00077325</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>0.0058687</t>
+          <t>0.00566475</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr"/>
@@ -16362,17 +16370,17 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="L62" s="4" t="inlineStr">
+          <t>95</t>
+        </is>
+      </c>
+      <c r="L62" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>Encontró 13 de 37 candidatos esperados (13/37 ≈35%). Cubre un subconjunto relevante pero omite la mayoría de las entidades listadas.</t>
+          <t>Listado real es correcto pero es subconjunto de la esperada (13 perfiles vs ~39 esperados). Cubre bien los incluidos, pero omite muchos nombres.</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -16382,12 +16390,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>0.0013407</t>
+          <t>0.0007505</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>0.00721545</t>
+          <t>0.00662525</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr"/>
@@ -16455,22 +16463,22 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="L63" s="4" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>Reporta 7 de 16 esperados (7/16 ≈44%). Cubre varios nombres clave pero deja fuera casi la mitad del listado esperado.</t>
+          <t>Se identifican 7 perfiles relevantes (todos válidos) pero faltan varios esperados (7/16). Responde bien la pregunta, con omisiones.</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -16480,12 +16488,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>0.0013407</t>
+          <t>0.0007505</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>0.0053622</t>
+          <t>0.004772</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr"/>
@@ -16573,22 +16581,22 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="L64" s="4" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L64" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>Incluye 17 perfiles que sí están en la lista esperada, pero la lista esperada tiene 112 entradas (17/112 ≈15%), cobertura muy parcial.</t>
+          <t>Se listan 17 perfiles válidos que hablan francés o alemán, pero la lista esperada es mucho mayor (~100); cubre una pequeña parte.</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -16598,12 +16606,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>0.0013407</t>
+          <t>0.0007505</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>0.0068137</t>
+          <t>0.0062235</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr"/>
@@ -16683,22 +16691,22 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="L65" s="4" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>Encontró 13 de 31 esperados (13/31 ≈42%). Buenas coincidencias puntuales pero faltan numerosos candidatos esperados.</t>
+          <t>Se encontraron 13 perfiles correctos (subconjunto de los ~31 esperados). respuesta directa y pertinente pero incompleta.</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -16708,12 +16716,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>0.0013407</t>
+          <t>0.0007505</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>0.00791845</t>
+          <t>0.00732825</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr"/>
@@ -16799,22 +16807,22 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="L66" s="5" t="inlineStr">
+          <t>95</t>
+        </is>
+      </c>
+      <c r="L66" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>Incluye 16 de 24 esperados (16/24 ≈67%). Cobertura mayoritaria pero aún omite varios nombres relevantes.</t>
+          <t>16/25 esperados aparecen; buena cobertura y respuesta clara sobre japonés o ruso, faltan algunos nombres esperados.</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -16824,12 +16832,12 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>0.0013407</t>
+          <t>0.0007505</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>0.0072927</t>
+          <t>0.0067025</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr"/>
@@ -16898,7 +16906,7 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L67" s="3" t="inlineStr">
@@ -16908,7 +16916,7 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>Coincidencia total: los 5 candidatos esperados están presentes (5/5).</t>
+          <t>Coincide exactamente con la lista esperada (5/5). Respuesta directa y completa sobre iOS/Android Developers.</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -16918,12 +16926,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>0.0013407</t>
+          <t>0.0007505</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>0.0058147</t>
+          <t>0.0052245</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr"/>
@@ -16992,7 +17000,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
@@ -17002,7 +17010,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>Coincidencia total: los 5 candidatos esperados aparecen en la respuesta real (5/5).</t>
+          <t>Coincide exactamente con la lista esperada (5/5). Respuesta clara y pertinente sobre Web/React Developers.</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -17012,12 +17020,12 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>0.0013407</t>
+          <t>0.0007505</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>0.00562145</t>
+          <t>0.00503125</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr"/>
@@ -17084,7 +17092,7 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L69" s="3" t="inlineStr">
@@ -17094,7 +17102,7 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>Coincidencia total: los 4 candidatos esperados están todos presentes (4/4).</t>
+          <t>Coincide exactamente con la lista esperada (4/4). Respuesta precisa y completa sobre Software Architect/Lead Developer.</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -17104,12 +17112,12 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>0.0013407</t>
+          <t>0.0007505</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>0.0052047</t>
+          <t>0.0046145</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr"/>
@@ -17183,22 +17191,22 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="L70" s="4" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L70" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>Incluye 10 de 27 esperados (10/27 ≈37%). Cubre varios casos pero falta gran parte del listado previsto.</t>
+          <t>Se identifican 10 perfiles relevantes (todos válidos) pero faltan muchos de la lista esperada (~27). Responde bien pero parcial.</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -17208,12 +17216,12 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>0.0013407</t>
+          <t>0.0007505</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>0.0072342</t>
+          <t>0.006644</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr"/>
@@ -17302,22 +17310,22 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="L71" s="4" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>Solo 6 de 43 esperados coinciden (6/43 ≈14%). La respuesta real contiene muchos perfiles distintos y omite la mayoría solicitada.</t>
+          <t>Se listan 17 perfiles con experiencia en datos (BERT no aparece explícito). Cobertura parcial respecto a la amplia lista esperada.</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -17327,12 +17335,12 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>0.0013407</t>
+          <t>0.0007505</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>0.0071952</t>
+          <t>0.006605</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr"/>
@@ -17414,22 +17422,22 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="L72" s="4" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L72" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>La respuesta real incluye 14 perfiles y coincide con 11 de los 23 esperados (~48%), omitiendo muchos nombres del gold standard.</t>
+          <t>Lista 14 perfiles; solo ~11 de los 24 esperados coinciden. Identifica correctamente perfiles con cloud/AWS Glue pero omite muchos nombres esperados.</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -17439,12 +17447,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>0.0010562</t>
+          <t>0.00123</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>0.00734995</t>
+          <t>0.00752375</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr"/>
@@ -17525,22 +17533,22 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="L73" s="4" t="inlineStr">
+          <t>85</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>Solo 6 de 22 esperados aparecen en la respuesta real (~27%), por tanto cobertura baja y faltan varios candidatos clave.</t>
+          <t>Presenta 13 perfiles, solo ~6 de los 22 esperados coinciden. Responde a DevOps/GitHub Flow pero deja fuera varios esperados.</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -17550,12 +17558,12 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>0.0010562</t>
+          <t>0.00123</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>0.0084127</t>
+          <t>0.0085865</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr"/>
@@ -17629,22 +17637,22 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="L74" s="4" t="inlineStr">
+          <t>95</t>
+        </is>
+      </c>
+      <c r="L74" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>Se encontraron 10 de 20 esperados (50%), cubre parcialmente pero deja fuera la otra mitad de la lista.</t>
+          <t>Incluye 10 perfiles, gran parte corresponden a la lista esperada (aprox. la mitad). Responde de forma directa y pertinente sobre microservicios.</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -17654,12 +17662,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>0.0010562</t>
+          <t>0.00123</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>0.00626845</t>
+          <t>0.00644225</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr"/>
@@ -17753,22 +17761,22 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="L75" s="4" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L75" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>Solo ~9–10 coincidencias frente a una lista extensa (~40), por tanto cobertura reducida y faltan muchos perfiles esperados.</t>
+          <t>Lista 20 perfiles relacionados con datos; cubre varios esperados pero falta una porción significativa. Responde claramente a la pregunta.</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -17778,12 +17786,12 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>0.0010562</t>
+          <t>0.00123</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>0.0087102</t>
+          <t>0.008884</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr"/>
@@ -17865,22 +17873,22 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="L76" s="4" t="inlineStr">
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L76" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>De 17 esperados, aparecen ~8 en la respuesta real (~47%), incluye varios no esperados y omite nombres relevantes.</t>
+          <t>Encuentra 14 perfiles cloud; aproximadamente la mitad de los esperados aparecen. Responde bien sobre experiencia cloud, con omisiones notables.</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -17890,12 +17898,12 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>0.0010562</t>
+          <t>0.00123</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>0.0067987</t>
+          <t>0.0069725</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr"/>
@@ -17984,17 +17992,17 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="L77" s="4" t="inlineStr">
+          <t>85</t>
+        </is>
+      </c>
+      <c r="L77" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>Respuesta real lista 15 perfiles pero solo ~7 coinciden con los 16 esperados (~44%), falta una parte significativa del gold standard.</t>
+          <t>15 perfiles señalados, varios coinciden con los esperados pero faltan nombres importantes. Responde sobre DevOps aunque incompleto.</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -18004,12 +18012,12 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>0.0010562</t>
+          <t>0.00123</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>0.00743645</t>
+          <t>0.00761025</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr"/>
@@ -18103,12 +18111,12 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L78" s="4" t="inlineStr">
@@ -18118,7 +18126,7 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>Gold espera 300 CVs; la respuesta indica 20. Discrepancia muy grande (≈7% de los esperados).</t>
+          <t>La respuesta da '20' CVs y lista perfiles, pero la pregunta pide el total (esperado 300). Respuesta numérica claramente incorrecta.</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -18128,12 +18136,12 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>0.0010562</t>
+          <t>0.00123</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>0.00594145</t>
+          <t>0.00611525</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr"/>
@@ -18224,12 +18232,12 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
@@ -18239,7 +18247,7 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>Se encontraron 16 puestos vs 167 esperados (~9.6%), por tanto la respuesta subestima drásticamente la cifra.</t>
+          <t>Indica 16 puestos distintos en lugar de 167 esperados; lista puestos pero la cuenta es muy inferior y no cubre la información requerida.</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -18249,12 +18257,12 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>0.0010562</t>
+          <t>0.00123</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>0.0088582</t>
+          <t>0.009032</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr"/>
@@ -18349,12 +18357,12 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>30</t>
         </is>
       </c>
       <c r="L80" s="4" t="inlineStr">
@@ -18364,7 +18372,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>Total informado 122 hard skills vs 643 esperadas (~19%), cobertura limitada y faltan muchas habilidades listadas.</t>
+          <t>Resume 122 hard skills distintas y 20 perfiles, pero el total esperado es 643. Responde al tipo de dato pedido pero con alcance muy inferior.</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -18374,12 +18382,12 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>0.0010562</t>
+          <t>0.00123</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>0.0100822</t>
+          <t>0.010256</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr"/>
@@ -18447,12 +18455,12 @@
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>30</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
@@ -18462,7 +18470,7 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>Solo 7 candidatos con ≥8 hard skills frente a 120 esperados (~5.8%), gran discrepancia y omisión significativa.</t>
+          <t>Dice 7 candidatos con ≥8 hard skills (evidencias incluidas) frente a 120 esperados: responde la pregunta pero el conteo es muy insuficiente.</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -18472,12 +18480,12 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>0.0010562</t>
+          <t>0.00123</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>0.0059557</t>
+          <t>0.0061295</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr"/>
@@ -18537,22 +18545,22 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="L82" s="4" t="inlineStr">
+          <t>85</t>
+        </is>
+      </c>
+      <c r="L82" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>Cuenta 3 candidatos cuando la respuesta esperada es 2: acierta en identificar perfiles pero el recuento es incorrecto (sobrecuenta 1).</t>
+          <t>Responde directamente con 3 perfiles pero el esperado es 2; coherente y detallada, aunque contradice el recuento esperado.</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -18562,12 +18570,12 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>0.0005487</t>
+          <t>0.00063925</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>0.0056657</t>
+          <t>0.00575625</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr"/>
@@ -18653,22 +18661,22 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="L83" s="4" t="inlineStr">
+          <t>70</t>
+        </is>
+      </c>
+      <c r="L83" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>Respuesta real lista 16 perfiles frente a 65 esperados: identifica algunas entidades correctas pero hay una subestimación muy grande.</t>
+          <t>Responde a la pregunta con 16 perfiles listados, formato adecuado, pero el total difiere ampliamente del esperado (65).</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -18678,12 +18686,12 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>0.0005487</t>
+          <t>0.00063925</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>0.00826195</t>
+          <t>0.0083525</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr"/>
@@ -18766,17 +18774,17 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="L84" s="5" t="inlineStr">
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>Coincide exactamente: 12 perfiles listados, mismos hechos y entidades que la respuesta esperada.</t>
+          <t>Coincide exactamente: 12 perfiles listados. Respuesta completa, directa y pertinente a la pregunta.</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -18786,12 +18794,12 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>0.0005487</t>
+          <t>0.00063925</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>0.0058842</t>
+          <t>0.00597475</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr"/>
@@ -18885,22 +18893,22 @@
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="L85" s="4" t="inlineStr">
+          <t>70</t>
+        </is>
+      </c>
+      <c r="L85" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>Solo 20 perfiles frente a 128 esperados: identificación muy parcial, falta la mayoría de entidades e información.</t>
+          <t>Da un recuento claro (20) y perfiles asociados, pero dista mucho del esperado (128); responde la pregunta aunque incompleta.</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -18910,12 +18918,12 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>0.0005487</t>
+          <t>0.00063925</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>0.00800345</t>
+          <t>0.008094</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr"/>
@@ -18989,22 +18997,22 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="L86" s="4" t="inlineStr">
+          <t>70</t>
+        </is>
+      </c>
+      <c r="L86" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>Encuentra 10 perfiles cuando se esperaban 22: acierta en ejemplos pero omite casi la mitad de los casos.</t>
+          <t>Identifica 10 perfiles con startups/hackathons y los describe; responde la pregunta pero omite muchos casos respecto al gold.</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -19014,12 +19022,12 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>0.0005487</t>
+          <t>0.00063925</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>0.0046262</t>
+          <t>0.00471675</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr"/>
@@ -19101,22 +19109,22 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="L87" s="4" t="inlineStr">
+          <t>70</t>
+        </is>
+      </c>
+      <c r="L87" s="5" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>Lista 14 perfiles frente a 36 esperados: identifica algunas coincidencias relevantes pero hay una subrepresentación notable.</t>
+          <t>Lista 14 perfiles con microservicios o cloud y aporta contexto; respuesta directa pero contiene menos casos que el esperado (36).</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -19126,12 +19134,12 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>0.0005487</t>
+          <t>0.00063925</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>0.00654395</t>
+          <t>0.0066345</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr"/>
